--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,6 +453,29 @@
         <is>
           <t>현재고</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -475,7 +475,7 @@
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,6 +476,29 @@
       </c>
       <c r="E2" t="n">
         <v>120</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -498,7 +498,7 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,6 +499,29 @@
       </c>
       <c r="E3" t="n">
         <v>36</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AR-F5103</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>70</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -521,7 +521,7 @@
         <v>70</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,6 +522,29 @@
       </c>
       <c r="E4" t="n">
         <v>120</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AR-F5103</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PALL</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>70</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -544,7 +544,7 @@
         <v>70</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -545,6 +545,29 @@
       </c>
       <c r="E5" t="n">
         <v>120</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7블럭</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HP-F8701</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -567,7 +567,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,6 +570,29 @@
         <v>24</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -593,6 +593,29 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7블럭</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HP-F8703</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,6 +616,29 @@
         <v>0</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PALL</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>70</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -636,7 +636,7 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,6 +639,29 @@
         <v>36</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AR-F5106</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -659,7 +659,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,29 +639,6 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>AR-F5106</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>15</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,6 +639,29 @@
         <v>36</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AR-F5106 (12"x300#)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -567,7 +567,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,12 +550,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7블럭</t>
+          <t>10블럭</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HP-F8701</t>
+          <t>AR-F5203</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -578,87 +578,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AR-F5203</t>
+          <t>AR-F5103A</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>신우</t>
+          <t>PALL</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7블럭</t>
+          <t>10블럭</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HP-F8703</t>
+          <t>AR-F5106 (12"x300#)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>신우</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>AR-F5103A</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>PALL</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>70</v>
-      </c>
-      <c r="E9" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>AR-F5106 (12"x300#)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
         <v>15</v>
       </c>
     </row>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,6 +616,29 @@
         <v>15</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7블럭</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HP-F8701 (12"x300#)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,6 +639,29 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7블럭</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HP-F8703 (12"x300#)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HP-F8701 필터같음</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -636,7 +636,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,6 +662,29 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PALL</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>40</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -682,7 +682,7 @@
         <v>40</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,6 +685,29 @@
         <v>18</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TG-F7103</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>50</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -705,7 +705,7 @@
         <v>50</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -567,7 +567,7 @@
         <v>50</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -567,7 +567,7 @@
         <v>50</v>
       </c>
       <c r="E6" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -521,7 +521,7 @@
         <v>70</v>
       </c>
       <c r="E4" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -521,7 +521,7 @@
         <v>70</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5">

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -521,7 +521,7 @@
         <v>70</v>
       </c>
       <c r="E4" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5">

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,11 @@
           <t>현재고</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>사용중</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -477,6 +482,9 @@
       <c r="E2" t="n">
         <v>120</v>
       </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -500,6 +508,9 @@
       <c r="E3" t="n">
         <v>36</v>
       </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -523,6 +534,9 @@
       <c r="E4" t="n">
         <v>240</v>
       </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -546,6 +560,9 @@
       <c r="E5" t="n">
         <v>120</v>
       </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -569,6 +586,9 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -592,6 +612,9 @@
       <c r="E7" t="n">
         <v>36</v>
       </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -615,6 +638,9 @@
       <c r="E8" t="n">
         <v>15</v>
       </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -638,6 +664,9 @@
       <c r="E9" t="n">
         <v>24</v>
       </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -661,6 +690,9 @@
       <c r="E10" t="n">
         <v>0</v>
       </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -684,6 +716,9 @@
       <c r="E11" t="n">
         <v>18</v>
       </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -706,6 +741,9 @@
       </c>
       <c r="E12" t="n">
         <v>30</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -509,7 +509,7 @@
         <v>36</v>
       </c>
       <c r="F3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -535,7 +535,7 @@
         <v>240</v>
       </c>
       <c r="F4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -639,7 +639,7 @@
         <v>15</v>
       </c>
       <c r="F8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -743,7 +743,7 @@
         <v>30</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -665,7 +665,7 @@
         <v>24</v>
       </c>
       <c r="F9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -691,7 +691,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -506,7 +506,7 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -506,7 +506,7 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -506,7 +506,7 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -506,7 +506,7 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -480,7 +480,7 @@
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -506,7 +506,7 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -506,7 +506,7 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>24</v>
+        <v>264</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>

--- a/filter_element_HOU.xlsx
+++ b/filter_element_HOU.xlsx
@@ -584,7 +584,7 @@
         <v>50</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
